--- a/it_forms/015_production_readiness_assessment--it_forms.xlsx
+++ b/it_forms/015_production_readiness_assessment--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -699,389 +699,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>risk_factors_10</t>
+          <t>submit_review</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk Factors 10</t>
+          <t>Submit Review</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>risk_factors_11</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Risk Factors 11</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>risk_factors_12</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Risk Factors 12</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>risk_factors_13</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Risk Factors 13</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>risk_factors_14</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Risk Factors 14</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>risk_factors_15</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Risk Factors 15</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>risk_factors_16</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Risk Factors 16</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>risk_factors_17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Risk Factors 17</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>risk_factors_18</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Risk Factors 18</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>review_comments</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Review Comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>go_live_reviewer</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Go Live Reviewer</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>reviewer_name</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Reviewer Name</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>reviewer_title</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Reviewer Title</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>review_date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Review Date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>review_time</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Review Time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>review_duration</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Review Duration</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit_review</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submit Review</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'risk_factor_1',_'label':_'risk_factor_1'}</t>
+          <t>risk_factor_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Risk Factor 1', 'label': 'Risk Factor 1'}</t>
+          <t>Risk Factor 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'risk_factor_2',_'label':_'risk_factor_2'}</t>
+          <t>risk_factor_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Risk Factor 2', 'label': 'Risk Factor 2'}</t>
+          <t>Risk Factor 2</t>
         </is>
       </c>
     </row>
@@ -1165,369 +797,131 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'risk_factor_3',_'label':_'risk_factor_3'}</t>
+          <t>risk_factor_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Risk Factor 3', 'label': 'Risk Factor 3'}</t>
+          <t>Risk Factor 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>risk_factors_10_choices</t>
+          <t>risk_factors_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'risk_factor_10_1',_'label':_'risk_factor_10_1'}</t>
+          <t>risk_factor_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Risk Factor 10 1', 'label': 'Risk Factor 10 1'}</t>
+          <t>Risk Factor 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>risk_factors_10_choices</t>
+          <t>risk_factors_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'risk_factor_10_2',_'label':_'risk_factor_10_2'}</t>
+          <t>risk_factor_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Risk Factor 10 2', 'label': 'Risk Factor 10 2'}</t>
+          <t>Risk Factor 5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>risk_factors_10_choices</t>
+          <t>risk_factors_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'risk_factor_10_3',_'label':_'risk_factor_10_3'}</t>
+          <t>risk_factor_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Risk Factor 10 3', 'label': 'Risk Factor 10 3'}</t>
+          <t>Risk Factor 6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>risk_factors_11_choices</t>
+          <t>risk_factors_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'risk_factor_11_1',_'label':_'risk_factor_11_1'}</t>
+          <t>risk_factor_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Risk Factor 11 1', 'label': 'Risk Factor 11 1'}</t>
+          <t>Risk Factor 7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>risk_factors_11_choices</t>
+          <t>risk_factors_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'risk_factor_11_2',_'label':_'risk_factor_11_2'}</t>
+          <t>risk_factor_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Risk Factor 11 2', 'label': 'Risk Factor 11 2'}</t>
+          <t>Risk Factor 8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>risk_factors_12_choices</t>
+          <t>submit_review_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'risk_factor_12_1',_'label':_'risk_factor_12_1'}</t>
+          <t>submit_review</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Risk Factor 12 1', 'label': 'Risk Factor 12 1'}</t>
+          <t>Submit Review</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>risk_factors_12_choices</t>
+          <t>submit_review_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'risk_factor_12_2',_'label':_'risk_factor_12_2'}</t>
+          <t>do_not_submit_review</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Risk Factor 12 2', 'label': 'Risk Factor 12 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>risk_factors_13_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'risk_factor_13_1',_'label':_'risk_factor_13_1'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Risk Factor 13 1', 'label': 'Risk Factor 13 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>risk_factors_13_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'risk_factor_13_2',_'label':_'risk_factor_13_2'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Risk Factor 13 2', 'label': 'Risk Factor 13 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>risk_factors_14_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'risk_factor_14_1',_'label':_'risk_factor_14_1'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Risk Factor 14 1', 'label': 'Risk Factor 14 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>risk_factors_14_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'risk_factor_14_2',_'label':_'risk_factor_14_2'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Risk Factor 14 2', 'label': 'Risk Factor 14 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>risk_factors_15_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'risk_factor_15_1',_'label':_'risk_factor_15_1'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Risk Factor 15 1', 'label': 'Risk Factor 15 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>risk_factors_15_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'risk_factor_15_2',_'label':_'risk_factor_15_2'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Risk Factor 15 2', 'label': 'Risk Factor 15 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>risk_factors_16_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'risk_factor_16_1',_'label':_'risk_factor_16_1'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Risk Factor 16 1', 'label': 'Risk Factor 16 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>risk_factors_16_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'risk_factor_16_2',_'label':_'risk_factor_16_2'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Risk Factor 16 2', 'label': 'Risk Factor 16 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>risk_factors_17_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'risk_factor_17_1',_'label':_'risk_factor_17_1'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Risk Factor 17 1', 'label': 'Risk Factor 17 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>risk_factors_17_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'risk_factor_17_2',_'label':_'risk_factor_17_2'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Risk Factor 17 2', 'label': 'Risk Factor 17 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>risk_factors_18_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'risk_factor_18_1',_'label':_'risk_factor_18_1'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Risk Factor 18 1', 'label': 'Risk Factor 18 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>risk_factors_18_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'risk_factor_18_2',_'label':_'risk_factor_18_2'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Risk Factor 18 2', 'label': 'Risk Factor 18 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>submit_review_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'submit_review',_'label':_'submit_review'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Submit Review', 'label': 'Submit Review'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>submit_review_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'do_not_submit_review',_'label':_'do_not_submit_review'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Do Not Submit Review', 'label': 'Do Not Submit Review'}</t>
+          <t>Do Not Submit Review</t>
         </is>
       </c>
     </row>
